--- a/hotel_manager_forms/015_guest_house_registration_form--hotel_manager_forms.xlsx
+++ b/hotel_manager_forms/015_guest_house_registration_form--hotel_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Postal Code</t>
+          <t>Postal Code 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Timezone Offset</t>
+          <t>Timezone Offset (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>timezone_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Timezone</t>
+          <t>Timezone 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Country Iso Code</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Timezone Offset</t>
+          <t>Timezone Offset (3)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Timezone Offset</t>
+          <t>Timezone Offset (4)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>America/New_York</t>
+          <t>America/New York</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>America/Los Angeles</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>America/Mexico_City</t>
+          <t>America/Mexico City</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>america/denver</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>America/Denver</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>korean</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Korean</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>korean</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>arabic</t>
+          <t>russian</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Russian</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>russian</t>
+          <t>hindi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>language_choices</t>
+          <t>currency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hindi</t>
+          <t>euro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Euro</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>euro</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>gbp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gbp</t>
+          <t>cny</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
     </row>
@@ -1505,146 +1505,129 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cny</t>
+          <t>jpy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>JPY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>currency_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jpy</t>
+          <t>america/new_york</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>America/New York</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>america/new_york</t>
+          <t>america/los_angeles</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>America/New_York</t>
+          <t>America/Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>america/los_angeles</t>
+          <t>america/mexico_city</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>America/Mexico City</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>america/mexico_city</t>
+          <t>america/denver</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>America/Mexico_City</t>
+          <t>America/Denver</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>america/denver</t>
+          <t>america/phoenix</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>America/Denver</t>
+          <t>America/Phoenix</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>america/phoenix</t>
+          <t>america/indianapolis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>America/Phoenix</t>
+          <t>America/Indianapolis</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>america/indianapolis</t>
+          <t>america/spokane</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>America/Indianapolis</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>america/spokane</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>America/Spokane</t>
         </is>
